--- a/IDIEW/bin/Debug/Plantillas/Plantilla.xlsx
+++ b/IDIEW/bin/Debug/Plantillas/Plantilla.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\capar\Documents\GitHub\IDEW\IDIEW\bin\Debug\Plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D597544D-7058-4BD4-9D8D-732879EAEE20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F962740-52DD-420B-AECB-3C03A63B5517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{57CA8308-0047-48D7-962C-C92FD17B13F4}"/>
   </bookViews>
@@ -617,12 +617,13 @@
     <col min="8" max="8" width="15.140625" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
     <col min="10" max="10" width="13.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" customWidth="1"/>
     <col min="13" max="13" width="14.7109375" customWidth="1"/>
     <col min="14" max="14" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>

--- a/IDIEW/bin/Debug/Plantillas/Plantilla.xlsx
+++ b/IDIEW/bin/Debug/Plantillas/Plantilla.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\capar\Documents\GitHub\IDEW\IDIEW\bin\Debug\Plantillas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\Documents\GitHub\IDEW\IDIEW\bin\Debug\Plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F962740-52DD-420B-AECB-3C03A63B5517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A8665FE-A71E-4D60-AA0F-B235EACE86A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{57CA8308-0047-48D7-962C-C92FD17B13F4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{57CA8308-0047-48D7-962C-C92FD17B13F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -219,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -227,22 +227,22 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -254,17 +254,11 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -308,9 +302,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -348,7 +342,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -454,7 +448,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -596,7 +590,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -605,19 +599,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91479835-8BF0-4788-BF9A-E13A50DE2EC4}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" customWidth="1"/>
     <col min="2" max="2" width="10.140625" customWidth="1"/>
-    <col min="3" max="3" width="6.5703125" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" customWidth="1"/>
     <col min="4" max="4" width="9.85546875" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" customWidth="1"/>
-    <col min="9" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" customWidth="1"/>
+    <col min="5" max="5" width="28.85546875" customWidth="1"/>
+    <col min="6" max="6" width="22.85546875" customWidth="1"/>
+    <col min="7" max="7" width="19.85546875" customWidth="1"/>
+    <col min="8" max="8" width="22.85546875" customWidth="1"/>
+    <col min="9" max="9" width="20.5703125" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
     <col min="11" max="11" width="14.42578125" customWidth="1"/>
+    <col min="12" max="12" width="21.140625" customWidth="1"/>
     <col min="13" max="13" width="14.7109375" customWidth="1"/>
     <col min="14" max="14" width="14.85546875" customWidth="1"/>
   </cols>
@@ -652,16 +647,16 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="258" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="18"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
+    <row r="3" spans="1:14" ht="309" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
     </row>
     <row r="4" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
@@ -740,21 +735,21 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="321" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="17"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
+    <row r="8" spans="1:14" ht="338.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
@@ -768,7 +763,7 @@
       <c r="I9" s="12"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="L9" s="14"/>
+      <c r="L9" s="7"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
     </row>
@@ -784,7 +779,7 @@
       <c r="I10" s="12"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="L10" s="14"/>
+      <c r="L10" s="7"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
     </row>
@@ -800,7 +795,7 @@
       <c r="I11" s="12"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="L11" s="14"/>
+      <c r="L11" s="7"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
     </row>
@@ -816,7 +811,7 @@
       <c r="I12" s="12"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="L12" s="14"/>
+      <c r="L12" s="7"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
     </row>
@@ -832,7 +827,7 @@
       <c r="I13" s="12"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="14"/>
+      <c r="L13" s="7"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
     </row>
@@ -848,7 +843,7 @@
       <c r="I14" s="12"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="L14" s="15"/>
+      <c r="L14" s="8"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
     </row>
@@ -864,7 +859,7 @@
       <c r="I15" s="12"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="L15" s="15"/>
+      <c r="L15" s="8"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
     </row>
@@ -880,7 +875,7 @@
       <c r="I16" s="12"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="L16" s="15"/>
+      <c r="L16" s="8"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
     </row>
@@ -896,7 +891,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="L17" s="15"/>
+      <c r="L17" s="8"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
     </row>
@@ -909,7 +904,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59D9ED59-8B4E-49B6-A5E3-BA55AD13657E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
